--- a/策划/数值文档/treasureclass_c.xlsx
+++ b/策划/数值文档/treasureclass_c.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <si>
     <t>name</t>
   </si>
@@ -512,6 +512,12 @@
   </si>
   <si>
     <t>hp1;4|hp2;8|hp3;5|mp2;2|mp3;5|rvs;1|vps;2|yps;3|wms;1</t>
+  </si>
+  <si>
+    <t>Quill 1</t>
+  </si>
+  <si>
+    <t>gld;19|Act 1 Junk;19</t>
   </si>
 </sst>
 </file>
@@ -3173,6 +3179,44 @@
         <v>0</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>166</v>
+      </c>
+      <c r="B63">
+        <v>16</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>125</v>
+      </c>
+      <c r="F63" t="s">
+        <v>167</v>
+      </c>
+      <c r="G63" t="s">
+        <v>93</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>